--- a/artfynd/A 17666-2026 artfynd.xlsx
+++ b/artfynd/A 17666-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY12"/>
+  <dimension ref="A1:AY18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>441614</v>
+        <v>166857</v>
       </c>
       <c r="B2" t="n">
-        <v>103261</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>104880</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,26 +686,26 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1662</v>
+        <v>563</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Bergviol</t>
+          <t>Sanddraba</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Viola collina</t>
+          <t>Draba nemorosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Besser</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>107</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -720,17 +715,17 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Torsboda beteshage (3), Mpd</t>
+          <t>Torsboda (1), Mpd</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>627620</v>
+        <v>627844</v>
       </c>
       <c r="R2" t="n">
-        <v>6935108</v>
+        <v>6935184</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -754,17 +749,17 @@
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>Y-Tim-0008</t>
+          <t>Y-Tim-0010</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2009-05-04</t>
+          <t>2005-05-31</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2009-05-04</t>
+          <t>2005-05-31</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -784,7 +779,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Y-län Floraväktarna, Gudrun Fredén, Olof Svensson</t>
+          <t>Y-län Floraväktarna, Stefan Grundström</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
@@ -795,15 +790,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>441617</v>
+        <v>7268753</v>
       </c>
       <c r="B3" t="n">
-        <v>103261</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>104880</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -811,43 +801,37 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1662</v>
+        <v>563</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Bergviol</t>
+          <t>Sanddraba</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Viola collina</t>
+          <t>Draba nemorosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Besser</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Torsboda beteshage (2), Mpd</t>
+          <t>Torsboda, Mpd</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>627774</v>
+        <v>627820</v>
       </c>
       <c r="R3" t="n">
-        <v>6935184</v>
+        <v>6935190</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -872,19 +856,14 @@
           <t>Hässjö</t>
         </is>
       </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>Y-Tim-0007</t>
-        </is>
-      </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2009-05-16</t>
+          <t>2014-04-28</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2009-05-16</t>
+          <t>2014-04-28</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -899,69 +878,66 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Y-län Floraväktarna</t>
+          <t>Margareta Edqvist</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Y-län Floraväktarna, Gudrun Fredén, Olof Svensson</t>
-        </is>
-      </c>
-      <c r="AY3" t="inlineStr">
-        <is>
-          <t>Floraväkteri Sverige</t>
-        </is>
-      </c>
+          <t>Margareta Edqvist</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>7268753</v>
+        <v>441397</v>
       </c>
       <c r="B4" t="n">
-        <v>101928</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>103673</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>563</v>
+        <v>1662</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Sanddraba</t>
+          <t>Bergviol</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Draba nemorosa</t>
+          <t>Viola collina</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
+          <t>Besser</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Torsboda, Mpd</t>
+          <t>Torsboda beteshage (3), Mpd</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>627819.7498970358</v>
+        <v>627620</v>
       </c>
       <c r="R4" t="n">
-        <v>6935189.706860023</v>
+        <v>6935108</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -986,24 +962,19 @@
           <t>Hässjö</t>
         </is>
       </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>Y-Tim-0008</t>
+        </is>
+      </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2014-04-28</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2007-05-16</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2014-04-28</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2007-05-16</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1018,31 +989,30 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Margareta Edqvist</t>
+          <t>Y-län Floraväktarna</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Margareta Edqvist</t>
-        </is>
-      </c>
-      <c r="AY4" t="inlineStr"/>
+          <t>Y-län Floraväktarna, Gudrun Fredén, Olof Svensson</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr">
+        <is>
+          <t>Floraväkteri Sverige</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>7268752</v>
+        <v>441617</v>
       </c>
       <c r="B5" t="n">
-        <v>101112</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>103673</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E5" t="n">
@@ -1063,20 +1033,26 @@
           <t>Besser</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Torsboda, Mpd</t>
+          <t>Torsboda beteshage (2), Mpd</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>627771.5626374072</v>
+        <v>627774</v>
       </c>
       <c r="R5" t="n">
-        <v>6935179.071736111</v>
+        <v>6935184</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1101,24 +1077,19 @@
           <t>Hässjö</t>
         </is>
       </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>Y-Tim-0007</t>
+        </is>
+      </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2014-04-28</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2009-05-16</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2014-04-28</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2009-05-16</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1133,49 +1104,48 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Margareta Edqvist</t>
+          <t>Y-län Floraväktarna</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Margareta Edqvist</t>
-        </is>
-      </c>
-      <c r="AY5" t="inlineStr"/>
+          <t>Y-län Floraväktarna, Gudrun Fredén, Olof Svensson</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr">
+        <is>
+          <t>Floraväkteri Sverige</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>7268747</v>
+        <v>7268752</v>
       </c>
       <c r="B6" t="n">
-        <v>107845</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>103673</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>222776</v>
+        <v>1662</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Desmeknopp</t>
+          <t>Bergviol</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Adoxa moschatellina</t>
+          <t>Viola collina</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Besser</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1188,13 +1158,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>627683.1838480056</v>
+        <v>627772</v>
       </c>
       <c r="R6" t="n">
-        <v>6935130.381040929</v>
+        <v>6935179</v>
       </c>
       <c r="S6" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1221,19 +1191,9 @@
           <t>2014-04-28</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2014-04-28</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1260,53 +1220,50 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>7268741</v>
+        <v>71945088</v>
       </c>
       <c r="B7" t="n">
-        <v>101128</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>103673</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>222009</v>
+        <v>1662</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Sandviol</t>
+          <t>Bergviol</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Viola rupestris</t>
+          <t>Viola collina</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>F. W. Schmidt</t>
+          <t>Besser</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Torsboda, Mpd</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>627771.5626374072</v>
+        <v>627791</v>
       </c>
       <c r="R7" t="n">
-        <v>6935179.071736111</v>
+        <v>6935184</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1333,22 +1290,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2014-04-28</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2018-06-01</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2014-04-28</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2018-06-01</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Ganska ymnig</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1359,31 +1311,31 @@
       </c>
       <c r="AG7" t="b">
         <v>0</v>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>Gles skog.</t>
+        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Margareta Edqvist</t>
+          <t>Jan Yngve Andersson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Margareta Edqvist</t>
+          <t>Jan Yngve Andersson, Olof Svensson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>16844384</v>
+        <v>16846182</v>
       </c>
       <c r="B8" t="n">
-        <v>103297</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>103697</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1391,22 +1343,26 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>224409</v>
+        <v>1665</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vanlig sandviol</t>
+          <t>Skuggviol</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Viola rupestris subsp. rupestris</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr"/>
+          <t>Viola selkirkii</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Pursh ex Goldie</t>
+        </is>
+      </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>26</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1422,17 +1378,17 @@
       <c r="L8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Torsboda (4), 270 m SV om västra gården, Mpd</t>
+          <t>Torsboda (6), 300 m SV om västra gården, Mpd</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>627805</v>
+        <v>627755</v>
       </c>
       <c r="R8" t="n">
-        <v>6935169</v>
+        <v>6935214</v>
       </c>
       <c r="S8" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1454,6 +1410,11 @@
           <t>Hässjö</t>
         </is>
       </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>Arkiv-Y-Tim-0043</t>
+        </is>
+      </c>
       <c r="Y8" t="inlineStr">
         <is>
           <t>2014-05-07</t>
@@ -1475,7 +1436,7 @@
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>Skogsbryn mot betesmark.</t>
+          <t>Gles skog.</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1486,79 +1447,71 @@
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Gudrun Fredén</t>
+          <t>Olof Svensson, Gudrun Fredén</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>Floraväkteri Sverige</t>
+          <t>Arkiv Floraväktarlokaler</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>16846182</v>
+        <v>94602779</v>
       </c>
       <c r="B9" t="n">
-        <v>103301</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>57340</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1665</v>
+        <v>100091</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Skuggviol</t>
+          <t>Storspov</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Viola selkirkii</t>
+          <t>Numenius arquata</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Pursh ex Goldie</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>26</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Torsboda (6), 300 m SV om västra gården, Mpd</t>
+          <t>Torsbodaängen, Söråker, Mpd</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>627755</v>
+        <v>627612</v>
       </c>
       <c r="R9" t="n">
-        <v>6935214</v>
+        <v>6935043</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1582,12 +1535,27 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2014-05-07</t>
+          <t>2021-07-01</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2014-05-07</t>
+          <t>2021-07-01</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>16:40</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Visade upp sig fint!!</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1598,40 +1566,26 @@
       </c>
       <c r="AG9" t="b">
         <v>0</v>
-      </c>
-      <c r="AI9" t="inlineStr">
-        <is>
-          <t>Gles skog.</t>
-        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Olof Svensson</t>
+          <t>Rode Nordin</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Olof Svensson, Gudrun Fredén</t>
-        </is>
-      </c>
-      <c r="AY9" t="inlineStr">
-        <is>
-          <t>Floraväkteri Sverige</t>
-        </is>
-      </c>
+          <t>Rode Nordin, Bruno Nordin</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>16844433</v>
+        <v>94602522</v>
       </c>
       <c r="B10" t="n">
-        <v>110138</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>43258</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1639,42 +1593,51 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>222776</v>
+        <v>201129</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Desmeknopp</t>
+          <t>Vitfläckig guldvinge</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Adoxa moschatellina</t>
+          <t>Lycaena virgaureae</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>imago/adult</t>
         </is>
       </c>
       <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Torsboda, (5), 300 m SV om västra gården, Mpd</t>
+          <t>Torsbodaängen, Söråker, Mpd</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>627739</v>
+        <v>627611</v>
       </c>
       <c r="R10" t="n">
-        <v>6935203</v>
+        <v>6935046</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1701,17 +1664,22 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2014-05-07</t>
+          <t>2021-07-01</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2014-05-07</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>200 kvm</t>
+          <t>2021-07-01</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>16:40</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1720,86 +1688,83 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
-      </c>
-      <c r="AI10" t="inlineStr">
-        <is>
-          <t>Gles lövskog.</t>
-        </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Olof Svensson</t>
+          <t>Bruno Nordin</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Olof Svensson, Gudrun Fredén</t>
-        </is>
-      </c>
-      <c r="AY10" t="inlineStr">
-        <is>
-          <t>Floraväkteri Sverige</t>
-        </is>
-      </c>
+          <t>Bruno Nordin, Rode Nordin</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>71945085</v>
+        <v>94603935</v>
       </c>
       <c r="B11" t="n">
-        <v>107845</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>43309</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>222776</v>
+        <v>201146</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Desmeknopp</t>
+          <t>Silverblåvinge</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Adoxa moschatellina</t>
+          <t>Polyommatus amandus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>(Schneider, 1792)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Torsboda, Mpd</t>
+          <t>Torsbodaängen, Söråker, Mpd</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>627743.3024419926</v>
+        <v>627612</v>
       </c>
       <c r="R11" t="n">
-        <v>6935203.865612491</v>
+        <v>6935043</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1823,27 +1788,22 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2018-06-01</t>
+          <t>2021-07-01</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2018-06-01</t>
+          <t>2021-07-01</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Åtskilliga kvadratmeter - heltäckande.</t>
+          <t>16:40</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1854,64 +1814,54 @@
       </c>
       <c r="AG11" t="b">
         <v>0</v>
-      </c>
-      <c r="AI11" t="inlineStr">
-        <is>
-          <t>Gles skog.</t>
-        </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Jan Yngve Andersson</t>
+          <t>Rode Nordin</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Jan Yngve Andersson, Olof Svensson</t>
+          <t>Rode Nordin, Bruno Nordin</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>71945088</v>
+        <v>71945087</v>
       </c>
       <c r="B12" t="n">
-        <v>101112</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
-        </is>
+        <v>101897</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1662</v>
+        <v>220075</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Bergviol</t>
+          <t>Gullpudra</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Viola collina</t>
+          <t>Chrysosplenium alternifolium</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Besser</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="K12" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>i frukt</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -1920,10 +1870,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>627791.2748561833</v>
+        <v>627770</v>
       </c>
       <c r="R12" t="n">
-        <v>6935183.989553377</v>
+        <v>6935177</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1953,26 +1903,11 @@
           <t>2018-06-01</t>
         </is>
       </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2018-06-01</t>
         </is>
       </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Ganska ymnig</t>
-        </is>
-      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
@@ -1984,7 +1919,7 @@
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>Gles skog.</t>
+          <t>Fuktig sluttning/källdrag. Gles skog</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -1999,6 +1934,682 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>56283751</v>
+      </c>
+      <c r="B13" t="n">
+        <v>106229</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>221725</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Ögonpyrola</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Moneses uniflora</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(L.) A. Gray</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>2100</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Torsboda, 500 m V om gården, Mpd</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>627663</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6935016</v>
+      </c>
+      <c r="S13" t="n">
+        <v>25</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Timrå</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Hässjö</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2015-07-13</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2015-07-13</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI13" t="inlineStr">
+        <is>
+          <t>Gles blandskog, kalkpåverkad</t>
+        </is>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Gudrun Fredén</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Gudrun Fredén</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>7268741</v>
+      </c>
+      <c r="B14" t="n">
+        <v>103691</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>222009</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Sandviol</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Viola rupestris</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>F. W. Schmidt</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Torsboda, Mpd</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>627772</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6935179</v>
+      </c>
+      <c r="S14" t="n">
+        <v>10</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Timrå</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Hässjö</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2014-04-28</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2014-04-28</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Margareta Edqvist</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Margareta Edqvist</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>7268747</v>
+      </c>
+      <c r="B15" t="n">
+        <v>111019</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>222776</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Desmeknopp</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Adoxa moschatellina</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Torsboda, Mpd</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>627683</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6935130</v>
+      </c>
+      <c r="S15" t="n">
+        <v>25</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Timrå</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Hässjö</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2014-04-28</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2014-04-28</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Margareta Edqvist</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Margareta Edqvist</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>16844433</v>
+      </c>
+      <c r="B16" t="n">
+        <v>111019</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>222776</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Desmeknopp</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Adoxa moschatellina</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Torsboda, (5), 300 m SV om västra gården, Mpd</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>627739</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6935203</v>
+      </c>
+      <c r="S16" t="n">
+        <v>25</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Timrå</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Hässjö</t>
+        </is>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>Arkiv-Y-Tim-0042</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2014-05-07</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2014-05-07</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>200 kvm</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF16" t="inlineStr"/>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI16" t="inlineStr">
+        <is>
+          <t>Gles lövskog.</t>
+        </is>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Olof Svensson</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Olof Svensson, Gudrun Fredén</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr">
+        <is>
+          <t>Arkiv Floraväktarlokaler</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>71945085</v>
+      </c>
+      <c r="B17" t="n">
+        <v>111019</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>222776</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Desmeknopp</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Adoxa moschatellina</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Torsboda, Mpd</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>627743</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6935204</v>
+      </c>
+      <c r="S17" t="n">
+        <v>10</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Timrå</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Hässjö</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2018-06-01</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2018-06-01</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Åtskilliga kvadratmeter - heltäckande.</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI17" t="inlineStr">
+        <is>
+          <t>Gles skog.</t>
+        </is>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Jan Yngve Andersson</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Jan Yngve Andersson, Olof Svensson</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>16844384</v>
+      </c>
+      <c r="B18" t="n">
+        <v>103693</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>224409</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Vanlig sandviol</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Viola rupestris subsp. rupestris</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr"/>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Torsboda (4), 270 m SV om västra gården, Mpd</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>627805</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6935169</v>
+      </c>
+      <c r="S18" t="n">
+        <v>25</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Timrå</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Hässjö</t>
+        </is>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>Arkiv-Y-Tim-0041</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2014-05-07</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2014-05-07</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI18" t="inlineStr">
+        <is>
+          <t>Skogsbryn mot betesmark.</t>
+        </is>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Olof Svensson</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Gudrun Fredén</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr">
+        <is>
+          <t>Arkiv Floraväktarlokaler</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 17666-2026 artfynd.xlsx
+++ b/artfynd/A 17666-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY18"/>
+  <dimension ref="A1:AZ18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -785,6 +790,11 @@
       <c r="AY2" t="inlineStr">
         <is>
           <t>Floraväkteri Sverige</t>
+        </is>
+      </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/166857</t>
         </is>
       </c>
     </row>
@@ -887,6 +897,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/7268753</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1002,6 +1017,11 @@
           <t>Floraväkteri Sverige</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/441397</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1115,6 +1135,11 @@
       <c r="AY5" t="inlineStr">
         <is>
           <t>Floraväkteri Sverige</t>
+        </is>
+      </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/441617</t>
         </is>
       </c>
     </row>
@@ -1217,6 +1242,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/7268752</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1329,6 +1359,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/71945088</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1455,6 +1490,11 @@
           <t>Arkiv Floraväktarlokaler</t>
         </is>
       </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/16846182</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1579,6 +1619,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/94602779</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1703,6 +1748,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/94602522</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1827,6 +1877,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/94603935</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1934,6 +1989,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/71945087</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2051,6 +2111,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/56283751</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2151,6 +2216,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/7268741</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2251,6 +2321,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/7268747</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2376,6 +2451,11 @@
           <t>Arkiv Floraväktarlokaler</t>
         </is>
       </c>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/16844433</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2488,6 +2568,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/71945085</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2610,8 +2695,32 @@
           <t>Arkiv Floraväktarlokaler</t>
         </is>
       </c>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/16844384</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>